--- a/单打评分实验记录.xlsx
+++ b/单打评分实验记录.xlsx
@@ -488,7 +488,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>中央民族大学匹克球俱乐部 · 单打评分实验记录</t>
+          <t>中央民族大学石榴籽体育管理 · 单打评分实验记录</t>
         </is>
       </c>
     </row>
@@ -669,6 +669,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2035,6 +2036,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2343,6 +2345,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2651,6 +2654,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2961,6 +2965,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3275,6 +3280,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3507,6 +3513,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
